--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.490816498502421</v>
+        <v>1.217257681006644</v>
       </c>
       <c r="D2" t="n">
-        <v>5.762146471723113</v>
+        <v>0.936348801655006</v>
       </c>
       <c r="E2" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F2" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.60560922034878</v>
+        <v>3.348411498306677</v>
       </c>
       <c r="D3" t="n">
-        <v>20.49847562745588</v>
+        <v>3.331002289461581</v>
       </c>
       <c r="E3" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F3" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.09958278792245</v>
+        <v>6.028682203037398</v>
       </c>
       <c r="D4" t="n">
-        <v>37.47734823356831</v>
+        <v>6.09006908795485</v>
       </c>
       <c r="E4" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F4" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.716138364925</v>
+        <v>9.216372484300313</v>
       </c>
       <c r="D5" t="n">
-        <v>56.94133447172211</v>
+        <v>9.252966851654843</v>
       </c>
       <c r="E5" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F5" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.64159296858239</v>
+        <v>2.866758857394639</v>
       </c>
       <c r="D6" t="n">
-        <v>35.06224623596029</v>
+        <v>5.697615013343547</v>
       </c>
       <c r="E6" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F6" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.49236488541955</v>
+        <v>7.067509293880677</v>
       </c>
       <c r="D7" t="n">
-        <v>49.97335039944304</v>
+        <v>8.120669439909493</v>
       </c>
       <c r="E7" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F7" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.78677033147658</v>
+        <v>4.190350178864945</v>
       </c>
       <c r="D8" t="n">
-        <v>26.10123306425331</v>
+        <v>4.241450372941163</v>
       </c>
       <c r="E8" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F8" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.48561031586433</v>
+        <v>3.003911676327953</v>
       </c>
       <c r="D9" t="n">
-        <v>17.0482625887212</v>
+        <v>2.770342670667195</v>
       </c>
       <c r="E9" t="n">
-        <v>15.09999193650612</v>
+        <v>2.453748689682245</v>
       </c>
       <c r="F9" t="n">
-        <v>16.03584073851625</v>
+        <v>2.605824120008891</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
